--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784650</v>
+        <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>92292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412364</v>
+        <v>412485</v>
       </c>
       <c r="R3" t="n">
-        <v>6966349</v>
+        <v>6966354</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/136828030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784655</v>
+        <v>135784650</v>
       </c>
       <c r="B4" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412389</v>
+        <v>412364</v>
       </c>
       <c r="R4" t="n">
-        <v>6966289</v>
+        <v>6966349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784651</v>
+        <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>83447</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412426</v>
       </c>
       <c r="R5" t="n">
-        <v>6966349</v>
+        <v>6966369</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/136828028</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784653</v>
+        <v>135784655</v>
       </c>
       <c r="B6" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412359</v>
+        <v>412389</v>
       </c>
       <c r="R6" t="n">
-        <v>6966319</v>
+        <v>6966289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348492</v>
+        <v>135784651</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>83447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412415</v>
+        <v>412364</v>
       </c>
       <c r="R7" t="n">
-        <v>6966371</v>
+        <v>6966349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,27 +1275,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348506</v>
+        <v>135784653</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412375</v>
+        <v>412359</v>
       </c>
       <c r="R8" t="n">
-        <v>6966295</v>
+        <v>6966319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,24 +1377,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348507</v>
+        <v>126348492</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412391</v>
+        <v>412415</v>
       </c>
       <c r="R9" t="n">
-        <v>6966325</v>
+        <v>6966371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,51 +1495,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784652</v>
+        <v>126348506</v>
       </c>
       <c r="B10" t="n">
-        <v>99350</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412369</v>
+        <v>412375</v>
       </c>
       <c r="R10" t="n">
-        <v>6966348</v>
+        <v>6966295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1566,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,27 +1591,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784654</v>
+        <v>126348507</v>
       </c>
       <c r="B11" t="n">
-        <v>80050</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412359</v>
+        <v>412391</v>
       </c>
       <c r="R11" t="n">
-        <v>6966324</v>
+        <v>6966325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,12 +1673,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784659</v>
+        <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,37 +1726,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412390</v>
+        <v>412417</v>
       </c>
       <c r="R12" t="n">
-        <v>6966336</v>
+        <v>6966372</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,12 +1785,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,65 +1810,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
+          <t>https://artportalen.se/Sighting/136828027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784656</v>
+        <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>98221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412402</v>
+        <v>412374</v>
       </c>
       <c r="R13" t="n">
-        <v>6966280</v>
+        <v>6966243</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,18 +1912,630 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966348</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784652</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784654</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412359</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6966324</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784654</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135784659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412390</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966336</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784659</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784656</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412402</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828029</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412423</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966366</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828029</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828031</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412490</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -1931,6 +2553,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828030</v>
+        <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>92292</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412485</v>
+        <v>412364</v>
       </c>
       <c r="R3" t="n">
-        <v>6966354</v>
+        <v>6966349</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828030</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784650</v>
+        <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>78863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412364</v>
+        <v>412389</v>
       </c>
       <c r="R4" t="n">
-        <v>6966349</v>
+        <v>6966289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828028</v>
+        <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>83447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412426</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6966369</v>
+        <v>6966349</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828028</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784655</v>
+        <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412389</v>
+        <v>412359</v>
       </c>
       <c r="R6" t="n">
-        <v>6966289</v>
+        <v>6966319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784651</v>
+        <v>126348492</v>
       </c>
       <c r="B7" t="n">
-        <v>83447</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412364</v>
+        <v>412415</v>
       </c>
       <c r="R7" t="n">
-        <v>6966349</v>
+        <v>6966371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1280,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784653</v>
+        <v>126348506</v>
       </c>
       <c r="B8" t="n">
-        <v>80079</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412359</v>
+        <v>412375</v>
       </c>
       <c r="R8" t="n">
-        <v>6966319</v>
+        <v>6966295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1362,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,24 +1387,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348492</v>
+        <v>126348507</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412415</v>
+        <v>412391</v>
       </c>
       <c r="R9" t="n">
-        <v>6966371</v>
+        <v>6966325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,51 +1505,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348506</v>
+        <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>99350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412375</v>
+        <v>412369</v>
       </c>
       <c r="R10" t="n">
-        <v>6966295</v>
+        <v>6966348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,17 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,27 +1596,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784652</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348507</v>
+        <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412391</v>
+        <v>412359</v>
       </c>
       <c r="R11" t="n">
-        <v>6966325</v>
+        <v>6966324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,17 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/135784654</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828027</v>
+        <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,42 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412417</v>
+        <v>412390</v>
       </c>
       <c r="R12" t="n">
-        <v>6966372</v>
+        <v>6966336</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,17 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,65 +1800,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828027</t>
+          <t>https://artportalen.se/Sighting/135784659</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136828026</v>
+        <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>98221</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>260591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412374</v>
+        <v>412402</v>
       </c>
       <c r="R13" t="n">
-        <v>6966243</v>
+        <v>6966280</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,630 +1902,18 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784652</v>
-      </c>
-      <c r="B14" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412369</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6966348</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784654</v>
-      </c>
-      <c r="B15" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412359</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6966324</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135784659</v>
-      </c>
-      <c r="B16" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412390</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6966336</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784656</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79483</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412402</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966280</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828029</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412423</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966366</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828029</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828031</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412490</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966358</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -2553,12 +1931,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828030</v>
+        <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>92303</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412485</v>
+        <v>412364</v>
       </c>
       <c r="R3" t="n">
-        <v>6966354</v>
+        <v>6966349</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828030</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784650</v>
+        <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>78863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412364</v>
+        <v>412389</v>
       </c>
       <c r="R4" t="n">
-        <v>6966349</v>
+        <v>6966289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828028</v>
+        <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>83447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412426</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6966369</v>
+        <v>6966349</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828028</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784655</v>
+        <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412389</v>
+        <v>412359</v>
       </c>
       <c r="R6" t="n">
-        <v>6966289</v>
+        <v>6966319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784651</v>
+        <v>126348492</v>
       </c>
       <c r="B7" t="n">
-        <v>83447</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412364</v>
+        <v>412415</v>
       </c>
       <c r="R7" t="n">
-        <v>6966349</v>
+        <v>6966371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1280,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784653</v>
+        <v>126348506</v>
       </c>
       <c r="B8" t="n">
-        <v>80079</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412359</v>
+        <v>412375</v>
       </c>
       <c r="R8" t="n">
-        <v>6966319</v>
+        <v>6966295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1362,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,24 +1387,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348492</v>
+        <v>126348507</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412415</v>
+        <v>412391</v>
       </c>
       <c r="R9" t="n">
-        <v>6966371</v>
+        <v>6966325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,51 +1505,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348506</v>
+        <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>99350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412375</v>
+        <v>412369</v>
       </c>
       <c r="R10" t="n">
-        <v>6966295</v>
+        <v>6966348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,17 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,27 +1596,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784652</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348507</v>
+        <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412391</v>
+        <v>412359</v>
       </c>
       <c r="R11" t="n">
-        <v>6966325</v>
+        <v>6966324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,17 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/135784654</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828027</v>
+        <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,42 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412417</v>
+        <v>412390</v>
       </c>
       <c r="R12" t="n">
-        <v>6966372</v>
+        <v>6966336</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,17 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,65 +1800,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828027</t>
+          <t>https://artportalen.se/Sighting/135784659</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136828026</v>
+        <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>98236</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>260591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412374</v>
+        <v>412402</v>
       </c>
       <c r="R13" t="n">
-        <v>6966243</v>
+        <v>6966280</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,630 +1902,18 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784652</v>
-      </c>
-      <c r="B14" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412369</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6966348</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784654</v>
-      </c>
-      <c r="B15" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412359</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6966324</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135784659</v>
-      </c>
-      <c r="B16" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412390</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6966336</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784656</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79483</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412402</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966280</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828029</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412423</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966366</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828029</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828031</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412490</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966358</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -2553,12 +1931,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784650</v>
+        <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>92307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412364</v>
+        <v>412485</v>
       </c>
       <c r="R3" t="n">
-        <v>6966349</v>
+        <v>6966354</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/136828030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784655</v>
+        <v>135784650</v>
       </c>
       <c r="B4" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412389</v>
+        <v>412364</v>
       </c>
       <c r="R4" t="n">
-        <v>6966289</v>
+        <v>6966349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784651</v>
+        <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>83447</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412426</v>
       </c>
       <c r="R5" t="n">
-        <v>6966349</v>
+        <v>6966369</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/136828028</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784653</v>
+        <v>135784655</v>
       </c>
       <c r="B6" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412359</v>
+        <v>412389</v>
       </c>
       <c r="R6" t="n">
-        <v>6966319</v>
+        <v>6966289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348492</v>
+        <v>135784651</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>83447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412415</v>
+        <v>412364</v>
       </c>
       <c r="R7" t="n">
-        <v>6966371</v>
+        <v>6966349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,27 +1275,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348506</v>
+        <v>135784653</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412375</v>
+        <v>412359</v>
       </c>
       <c r="R8" t="n">
-        <v>6966295</v>
+        <v>6966319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,24 +1377,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348507</v>
+        <v>126348492</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412391</v>
+        <v>412415</v>
       </c>
       <c r="R9" t="n">
-        <v>6966325</v>
+        <v>6966371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,51 +1495,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784652</v>
+        <v>126348506</v>
       </c>
       <c r="B10" t="n">
-        <v>99350</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412369</v>
+        <v>412375</v>
       </c>
       <c r="R10" t="n">
-        <v>6966348</v>
+        <v>6966295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1566,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,27 +1591,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784654</v>
+        <v>126348507</v>
       </c>
       <c r="B11" t="n">
-        <v>80050</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412359</v>
+        <v>412391</v>
       </c>
       <c r="R11" t="n">
-        <v>6966324</v>
+        <v>6966325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,12 +1673,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784659</v>
+        <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,37 +1726,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412390</v>
+        <v>412417</v>
       </c>
       <c r="R12" t="n">
-        <v>6966336</v>
+        <v>6966372</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,12 +1785,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,65 +1810,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
+          <t>https://artportalen.se/Sighting/136828027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784656</v>
+        <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>98240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412402</v>
+        <v>412374</v>
       </c>
       <c r="R13" t="n">
-        <v>6966280</v>
+        <v>6966243</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,18 +1912,630 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966348</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784652</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784654</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412359</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6966324</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784654</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135784659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412390</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966336</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784659</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784656</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412402</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828029</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412423</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966366</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828029</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828031</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412490</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -1931,6 +2553,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828030</v>
+        <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>92307</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412485</v>
+        <v>412364</v>
       </c>
       <c r="R3" t="n">
-        <v>6966354</v>
+        <v>6966349</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828030</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784650</v>
+        <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>78863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412364</v>
+        <v>412389</v>
       </c>
       <c r="R4" t="n">
-        <v>6966349</v>
+        <v>6966289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828028</v>
+        <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>83447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412426</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6966369</v>
+        <v>6966349</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828028</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784655</v>
+        <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>78863</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412389</v>
+        <v>412359</v>
       </c>
       <c r="R6" t="n">
-        <v>6966289</v>
+        <v>6966319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135784651</v>
+        <v>126348492</v>
       </c>
       <c r="B7" t="n">
-        <v>83447</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412364</v>
+        <v>412415</v>
       </c>
       <c r="R7" t="n">
-        <v>6966349</v>
+        <v>6966371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1280,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784653</v>
+        <v>126348506</v>
       </c>
       <c r="B8" t="n">
-        <v>80079</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412359</v>
+        <v>412375</v>
       </c>
       <c r="R8" t="n">
-        <v>6966319</v>
+        <v>6966295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1362,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,24 +1387,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348492</v>
+        <v>126348507</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412415</v>
+        <v>412391</v>
       </c>
       <c r="R9" t="n">
-        <v>6966371</v>
+        <v>6966325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,51 +1505,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348506</v>
+        <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>99350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412375</v>
+        <v>412369</v>
       </c>
       <c r="R10" t="n">
-        <v>6966295</v>
+        <v>6966348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,17 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,27 +1596,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784652</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348507</v>
+        <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412391</v>
+        <v>412359</v>
       </c>
       <c r="R11" t="n">
-        <v>6966325</v>
+        <v>6966324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,17 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/135784654</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136828027</v>
+        <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,42 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412417</v>
+        <v>412390</v>
       </c>
       <c r="R12" t="n">
-        <v>6966372</v>
+        <v>6966336</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,17 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,65 +1800,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828027</t>
+          <t>https://artportalen.se/Sighting/135784659</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136828026</v>
+        <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>260591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412374</v>
+        <v>412402</v>
       </c>
       <c r="R13" t="n">
-        <v>6966243</v>
+        <v>6966280</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,630 +1902,18 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135784652</v>
-      </c>
-      <c r="B14" t="n">
-        <v>99350</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412369</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6966348</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135784654</v>
-      </c>
-      <c r="B15" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412359</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6966324</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135784659</v>
-      </c>
-      <c r="B16" t="n">
-        <v>80050</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412390</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6966336</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135784656</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79483</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412402</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6966280</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828029</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412423</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6966366</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828029</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828031</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412490</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6966358</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -2553,12 +1931,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784650</v>
+        <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>92309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412364</v>
+        <v>412485</v>
       </c>
       <c r="R3" t="n">
-        <v>6966349</v>
+        <v>6966354</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +867,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784650</t>
+          <t>https://artportalen.se/Sighting/136828030</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784655</v>
+        <v>135784650</v>
       </c>
       <c r="B4" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412389</v>
+        <v>412364</v>
       </c>
       <c r="R4" t="n">
-        <v>6966289</v>
+        <v>6966349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784655</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784651</v>
+        <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>83447</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412426</v>
       </c>
       <c r="R5" t="n">
-        <v>6966349</v>
+        <v>6966369</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784651</t>
+          <t>https://artportalen.se/Sighting/136828028</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784653</v>
+        <v>135784655</v>
       </c>
       <c r="B6" t="n">
-        <v>80079</v>
+        <v>78863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412359</v>
+        <v>412389</v>
       </c>
       <c r="R6" t="n">
-        <v>6966319</v>
+        <v>6966289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784653</t>
+          <t>https://artportalen.se/Sighting/135784655</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348492</v>
+        <v>135784651</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>83447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412415</v>
+        <v>412364</v>
       </c>
       <c r="R7" t="n">
-        <v>6966371</v>
+        <v>6966349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,27 +1275,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/135784651</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348506</v>
+        <v>135784653</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412375</v>
+        <v>412359</v>
       </c>
       <c r="R8" t="n">
-        <v>6966295</v>
+        <v>6966319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,24 +1377,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784653</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348507</v>
+        <v>126348492</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412391</v>
+        <v>412415</v>
       </c>
       <c r="R9" t="n">
-        <v>6966325</v>
+        <v>6966371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,51 +1495,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348507</t>
+          <t>https://artportalen.se/Sighting/126348492</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784652</v>
+        <v>126348506</v>
       </c>
       <c r="B10" t="n">
-        <v>99350</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412369</v>
+        <v>412375</v>
       </c>
       <c r="R10" t="n">
-        <v>6966348</v>
+        <v>6966295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1566,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,27 +1591,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784652</t>
+          <t>https://artportalen.se/Sighting/126348506</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784654</v>
+        <v>126348507</v>
       </c>
       <c r="B11" t="n">
-        <v>80050</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412359</v>
+        <v>412391</v>
       </c>
       <c r="R11" t="n">
-        <v>6966324</v>
+        <v>6966325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,12 +1673,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,27 +1698,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784654</t>
+          <t>https://artportalen.se/Sighting/126348507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784659</v>
+        <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,37 +1726,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412390</v>
+        <v>412417</v>
       </c>
       <c r="R12" t="n">
-        <v>6966336</v>
+        <v>6966372</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,12 +1785,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,65 +1810,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784659</t>
+          <t>https://artportalen.se/Sighting/136828027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135784656</v>
+        <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>98244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412402</v>
+        <v>412374</v>
       </c>
       <c r="R13" t="n">
-        <v>6966280</v>
+        <v>6966243</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,18 +1912,630 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966348</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784652</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784654</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412359</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6966324</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784654</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135784659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412390</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966336</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784659</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135784656</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412402</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784656</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828029</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412423</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966366</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828029</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828031</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412490</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966358</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828031</t>
         </is>
       </c>
     </row>
@@ -1931,6 +2553,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -1744,11 +1744,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>136828027</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136828030</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828028</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136828026</v>
       </c>
       <c r="B13" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>136828029</v>
       </c>
       <c r="B18" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>136828031</v>
       </c>
       <c r="B19" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
